--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P217"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12174,6 +12174,60 @@
       <c r="P217" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>351.32</v>
+      </c>
+      <c r="C218" t="n">
+        <v>332.85</v>
+      </c>
+      <c r="D218" t="n">
+        <v>317.52</v>
+      </c>
+      <c r="E218" t="n">
+        <v>318.67</v>
+      </c>
+      <c r="F218" t="n">
+        <v>319.23</v>
+      </c>
+      <c r="G218" t="n">
+        <v>320.61</v>
+      </c>
+      <c r="H218" t="n">
+        <v>316.72</v>
+      </c>
+      <c r="I218" t="n">
+        <v>317.03</v>
+      </c>
+      <c r="J218" t="n">
+        <v>323.81</v>
+      </c>
+      <c r="K218" t="n">
+        <v>331.9</v>
+      </c>
+      <c r="L218" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="M218" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>345.91</v>
+      </c>
+      <c r="O218" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14391,6 +14445,16 @@
       </c>
       <c r="B220" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -14559,28 +14623,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3041764887717804</v>
+        <v>-0.307176134283257</v>
       </c>
       <c r="J2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08669108758351229</v>
+        <v>0.08902550559300926</v>
       </c>
       <c r="M2" t="n">
-        <v>6.248599402408542</v>
+        <v>6.23662596705717</v>
       </c>
       <c r="N2" t="n">
-        <v>60.98120412546402</v>
+        <v>60.75435908436782</v>
       </c>
       <c r="O2" t="n">
-        <v>7.809046300635182</v>
+        <v>7.794508264436431</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8582856817243</v>
+        <v>362.8865618248127</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14637,28 +14701,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4627255941327572</v>
+        <v>-0.4706867157380483</v>
       </c>
       <c r="J3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09445496776096474</v>
+        <v>0.0980677536016229</v>
       </c>
       <c r="M3" t="n">
-        <v>9.01287553884355</v>
+        <v>9.014144448649711</v>
       </c>
       <c r="N3" t="n">
-        <v>128.4203231423713</v>
+        <v>128.2101190162537</v>
       </c>
       <c r="O3" t="n">
-        <v>11.33226910827533</v>
+        <v>11.32299072755311</v>
       </c>
       <c r="P3" t="n">
-        <v>354.3250924725364</v>
+        <v>354.4001379446743</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14715,28 +14779,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3997025499295088</v>
+        <v>-0.4115495711448457</v>
       </c>
       <c r="J4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05745749673733269</v>
+        <v>0.06100320879141718</v>
       </c>
       <c r="M4" t="n">
-        <v>10.4428111503773</v>
+        <v>10.44026625532755</v>
       </c>
       <c r="N4" t="n">
-        <v>163.9568428145303</v>
+        <v>164.0463111468912</v>
       </c>
       <c r="O4" t="n">
-        <v>12.80456335899551</v>
+        <v>12.80805649374218</v>
       </c>
       <c r="P4" t="n">
-        <v>341.7959014096631</v>
+        <v>341.9075772946217</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14793,28 +14857,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4819246241225842</v>
+        <v>-0.489790115779874</v>
       </c>
       <c r="J5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07670254959118339</v>
+        <v>0.07963046469473423</v>
       </c>
       <c r="M5" t="n">
-        <v>10.51483949572388</v>
+        <v>10.50558919757518</v>
       </c>
       <c r="N5" t="n">
-        <v>174.9006958973453</v>
+        <v>174.4671840455515</v>
       </c>
       <c r="O5" t="n">
-        <v>13.22500268042866</v>
+        <v>13.20860265302699</v>
       </c>
       <c r="P5" t="n">
-        <v>340.5426062447028</v>
+        <v>340.6167502616244</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14871,28 +14935,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5887743953504865</v>
+        <v>-0.5932069777149792</v>
       </c>
       <c r="J6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1068689655167433</v>
+        <v>0.1092535974445292</v>
       </c>
       <c r="M6" t="n">
-        <v>10.28936209015588</v>
+        <v>10.26707540319972</v>
       </c>
       <c r="N6" t="n">
-        <v>181.2436801370377</v>
+        <v>180.5267510613076</v>
       </c>
       <c r="O6" t="n">
-        <v>13.46267730197221</v>
+        <v>13.43602437707328</v>
       </c>
       <c r="P6" t="n">
-        <v>339.994547046713</v>
+        <v>340.0363307617253</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14949,28 +15013,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4076642979278836</v>
+        <v>-0.4112706370398282</v>
       </c>
       <c r="J7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05567154695487253</v>
+        <v>0.05713861181705904</v>
       </c>
       <c r="M7" t="n">
-        <v>9.949179214256752</v>
+        <v>9.923320378950416</v>
       </c>
       <c r="N7" t="n">
-        <v>176.3585869527456</v>
+        <v>175.6241790895284</v>
       </c>
       <c r="O7" t="n">
-        <v>13.28000703888163</v>
+        <v>13.25232730842128</v>
       </c>
       <c r="P7" t="n">
-        <v>335.5987208083608</v>
+        <v>335.6327159455743</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15027,28 +15091,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4345428317330401</v>
+        <v>-0.4390394317834068</v>
       </c>
       <c r="J8" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K8" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05219921552369466</v>
+        <v>0.05372469866202723</v>
       </c>
       <c r="M8" t="n">
-        <v>11.24575550590576</v>
+        <v>11.21742688142601</v>
       </c>
       <c r="N8" t="n">
-        <v>214.4962651303717</v>
+        <v>213.6295399752103</v>
       </c>
       <c r="O8" t="n">
-        <v>14.64569100897502</v>
+        <v>14.61607129071319</v>
       </c>
       <c r="P8" t="n">
-        <v>333.4515398572624</v>
+        <v>333.4939270346635</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15105,28 +15169,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3139176074458103</v>
+        <v>-0.3190304770800788</v>
       </c>
       <c r="J9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03087357226080423</v>
+        <v>0.03215193893708912</v>
       </c>
       <c r="M9" t="n">
-        <v>10.70753400274084</v>
+        <v>10.68137881540215</v>
       </c>
       <c r="N9" t="n">
-        <v>193.5202301846708</v>
+        <v>192.7858240654994</v>
       </c>
       <c r="O9" t="n">
-        <v>13.91115488321048</v>
+        <v>13.88473348917794</v>
       </c>
       <c r="P9" t="n">
-        <v>331.2666931341599</v>
+        <v>331.3148895736451</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15183,28 +15247,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3657825734721484</v>
+        <v>-0.3696488146573957</v>
       </c>
       <c r="J10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04735705824496561</v>
+        <v>0.04877022126465747</v>
       </c>
       <c r="M10" t="n">
-        <v>9.851181593791749</v>
+        <v>9.821774268992145</v>
       </c>
       <c r="N10" t="n">
-        <v>168.3809386167796</v>
+        <v>167.6949873276956</v>
       </c>
       <c r="O10" t="n">
-        <v>12.97616810220874</v>
+        <v>12.94970993218364</v>
       </c>
       <c r="P10" t="n">
-        <v>337.9920185487619</v>
+        <v>338.0284636515415</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15261,28 +15325,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2446785710427404</v>
+        <v>-0.2489922987440199</v>
       </c>
       <c r="J11" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K11" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02296743351192831</v>
+        <v>0.02399086051905108</v>
       </c>
       <c r="M11" t="n">
-        <v>9.886253197983207</v>
+        <v>9.866368483061089</v>
       </c>
       <c r="N11" t="n">
-        <v>159.3271947737406</v>
+        <v>158.7050044727461</v>
       </c>
       <c r="O11" t="n">
-        <v>12.62248766185733</v>
+        <v>12.59781744877842</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3781587517695</v>
+        <v>343.4188220839064</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15339,28 +15403,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.341377273672172</v>
+        <v>-0.3399213375822049</v>
       </c>
       <c r="J12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04098257708526576</v>
+        <v>0.04105234079052844</v>
       </c>
       <c r="M12" t="n">
-        <v>10.78814776199338</v>
+        <v>10.74404612456278</v>
       </c>
       <c r="N12" t="n">
-        <v>170.6074182113767</v>
+        <v>169.8339714864021</v>
       </c>
       <c r="O12" t="n">
-        <v>13.06167746544741</v>
+        <v>13.0320363522514</v>
       </c>
       <c r="P12" t="n">
-        <v>351.2133646564394</v>
+        <v>351.1996402823259</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15417,28 +15481,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2102298411117189</v>
+        <v>-0.2116055288697138</v>
       </c>
       <c r="J13" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K13" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01566342722014324</v>
+        <v>0.01602794608461722</v>
       </c>
       <c r="M13" t="n">
-        <v>10.27389244911534</v>
+        <v>10.23521690577833</v>
       </c>
       <c r="N13" t="n">
-        <v>173.7588841062248</v>
+        <v>172.9695463735206</v>
       </c>
       <c r="O13" t="n">
-        <v>13.18176331551378</v>
+        <v>13.1517887138412</v>
       </c>
       <c r="P13" t="n">
-        <v>354.2759787954078</v>
+        <v>354.28894670903</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15495,28 +15559,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3507783951021184</v>
+        <v>-0.3541833720870291</v>
       </c>
       <c r="J14" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0369373811538084</v>
+        <v>0.0379964012331907</v>
       </c>
       <c r="M14" t="n">
-        <v>11.24853242494636</v>
+        <v>11.21775261404975</v>
       </c>
       <c r="N14" t="n">
-        <v>200.7037862138875</v>
+        <v>199.8486882552229</v>
       </c>
       <c r="O14" t="n">
-        <v>14.16699637233974</v>
+        <v>14.13678493347136</v>
       </c>
       <c r="P14" t="n">
-        <v>359.1551796469381</v>
+        <v>359.1872766450899</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15573,28 +15637,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6217906856308948</v>
+        <v>-0.6209088575611303</v>
       </c>
       <c r="J15" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K15" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09215227310471208</v>
+        <v>0.09278489447580307</v>
       </c>
       <c r="M15" t="n">
-        <v>12.50229758175612</v>
+        <v>12.4483639036352</v>
       </c>
       <c r="N15" t="n">
-        <v>238.2850792828496</v>
+        <v>237.191673253493</v>
       </c>
       <c r="O15" t="n">
-        <v>15.43648532804179</v>
+        <v>15.40102831805373</v>
       </c>
       <c r="P15" t="n">
-        <v>365.579868720791</v>
+        <v>365.5715561729968</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15632,7 +15696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P217"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33429,6 +33493,88 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>-34.45491387727594,173.0034730846862</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>-34.455650770178316,173.00325232437586</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-34.45638827684617,173.0030657381127</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-34.45712903450134,173.00305852835479</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-34.45786966896187,173.00304489680323</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-34.45861045895002,173.00304019095074</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-34.45934277552148,173.00297840224022</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-34.460067559863475,173.00293229447365</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-34.46080369895007,173.0029266499812</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-34.461547911522565,173.00293450793038</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-34.4622983243889,173.00298346900465</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-34.46304485956055,173.00296887260654</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-34.46378770531752,173.0029354169439</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-34.46452900602708,173.00296019461516</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P218"/>
+  <dimension ref="A1:P219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12223,11 +12223,65 @@
         <v>345.91</v>
       </c>
       <c r="O218" t="n">
-        <v>350.06</v>
+        <v>343.2</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="C219" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="D219" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="E219" t="n">
+        <v>320.07</v>
+      </c>
+      <c r="F219" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="G219" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="H219" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="I219" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="J219" t="n">
+        <v>323.92</v>
+      </c>
+      <c r="K219" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="L219" t="n">
+        <v>339.66</v>
+      </c>
+      <c r="M219" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="N219" t="n">
+        <v>344.84</v>
+      </c>
+      <c r="O219" t="n">
+        <v>341.83</v>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B221"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14455,6 +14509,16 @@
       </c>
       <c r="B221" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -14623,28 +14687,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.307176134283257</v>
+        <v>-0.3102317437289098</v>
       </c>
       <c r="J2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08902550559300926</v>
+        <v>0.09142595210104676</v>
       </c>
       <c r="M2" t="n">
-        <v>6.23662596705717</v>
+        <v>6.225005320982936</v>
       </c>
       <c r="N2" t="n">
-        <v>60.75435908436782</v>
+        <v>60.532279514085</v>
       </c>
       <c r="O2" t="n">
-        <v>7.794508264436431</v>
+        <v>7.780249322103052</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8865618248127</v>
+        <v>362.9155139270673</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14701,28 +14765,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4706867157380483</v>
+        <v>-0.4767263670721363</v>
       </c>
       <c r="J3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0980677536016229</v>
+        <v>0.1011302988876012</v>
       </c>
       <c r="M3" t="n">
-        <v>9.014144448649711</v>
+        <v>9.005387804788946</v>
       </c>
       <c r="N3" t="n">
-        <v>128.2101190162537</v>
+        <v>127.8431672373184</v>
       </c>
       <c r="O3" t="n">
-        <v>11.32299072755311</v>
+        <v>11.30677528021666</v>
       </c>
       <c r="P3" t="n">
-        <v>354.4001379446743</v>
+        <v>354.45736404183</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14779,28 +14843,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4115495711448457</v>
+        <v>-0.4204226968241572</v>
       </c>
       <c r="J4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06100320879141718</v>
+        <v>0.06393857114805768</v>
       </c>
       <c r="M4" t="n">
-        <v>10.44026625532755</v>
+        <v>10.42604827770781</v>
       </c>
       <c r="N4" t="n">
-        <v>164.0463111468912</v>
+        <v>163.7711715748207</v>
       </c>
       <c r="O4" t="n">
-        <v>12.80805649374218</v>
+        <v>12.79731110721392</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9075772946217</v>
+        <v>341.9916507492156</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14857,28 +14921,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.489790115779874</v>
+        <v>-0.4962424223178754</v>
       </c>
       <c r="J5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07963046469473423</v>
+        <v>0.08224169438470197</v>
       </c>
       <c r="M5" t="n">
-        <v>10.50558919757518</v>
+        <v>10.48926824058564</v>
       </c>
       <c r="N5" t="n">
-        <v>174.4671840455515</v>
+        <v>173.9192986757172</v>
       </c>
       <c r="O5" t="n">
-        <v>13.20860265302699</v>
+        <v>13.1878466276992</v>
       </c>
       <c r="P5" t="n">
-        <v>340.6167502616244</v>
+        <v>340.6778862942193</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14935,28 +14999,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5932069777149792</v>
+        <v>-0.5981286022996789</v>
       </c>
       <c r="J6" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K6" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1092535974445292</v>
+        <v>0.1118188031810459</v>
       </c>
       <c r="M6" t="n">
-        <v>10.26707540319972</v>
+        <v>10.24751394956612</v>
       </c>
       <c r="N6" t="n">
-        <v>180.5267510613076</v>
+        <v>179.845510777766</v>
       </c>
       <c r="O6" t="n">
-        <v>13.43602437707328</v>
+        <v>13.41064915571823</v>
       </c>
       <c r="P6" t="n">
-        <v>340.0363307617253</v>
+        <v>340.0829634812432</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15013,28 +15077,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4112706370398282</v>
+        <v>-0.4155790599939577</v>
       </c>
       <c r="J7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05713861181705904</v>
+        <v>0.0588087393224439</v>
       </c>
       <c r="M7" t="n">
-        <v>9.923320378950416</v>
+        <v>9.901500039386024</v>
       </c>
       <c r="N7" t="n">
-        <v>175.6241790895284</v>
+        <v>174.9311109413073</v>
       </c>
       <c r="O7" t="n">
-        <v>13.25232730842128</v>
+        <v>13.22615253735217</v>
       </c>
       <c r="P7" t="n">
-        <v>335.6327159455743</v>
+        <v>335.6735385389532</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15091,28 +15155,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4390394317834068</v>
+        <v>-0.4431799502471531</v>
       </c>
       <c r="J8" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K8" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05372469866202723</v>
+        <v>0.0552009556450106</v>
       </c>
       <c r="M8" t="n">
-        <v>11.21742688142601</v>
+        <v>11.18750038048287</v>
       </c>
       <c r="N8" t="n">
-        <v>213.6295399752103</v>
+        <v>212.7535340263075</v>
       </c>
       <c r="O8" t="n">
-        <v>14.61607129071319</v>
+        <v>14.58607329017332</v>
       </c>
       <c r="P8" t="n">
-        <v>333.4939270346635</v>
+        <v>333.5331587218545</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15169,28 +15233,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3190304770800788</v>
+        <v>-0.3242693797336912</v>
       </c>
       <c r="J9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03215193893708912</v>
+        <v>0.03348791569088005</v>
       </c>
       <c r="M9" t="n">
-        <v>10.68137881540215</v>
+        <v>10.65580844415375</v>
       </c>
       <c r="N9" t="n">
-        <v>192.7858240654994</v>
+        <v>192.0678953681691</v>
       </c>
       <c r="O9" t="n">
-        <v>13.88473348917794</v>
+        <v>13.85885620706735</v>
       </c>
       <c r="P9" t="n">
-        <v>331.3148895736451</v>
+        <v>331.3645285239191</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15247,28 +15311,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3696488146573957</v>
+        <v>-0.3733098599932099</v>
       </c>
       <c r="J10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04877022126465747</v>
+        <v>0.05016228982794457</v>
       </c>
       <c r="M10" t="n">
-        <v>9.821774268992145</v>
+        <v>9.792170207400638</v>
       </c>
       <c r="N10" t="n">
-        <v>167.6949873276956</v>
+        <v>167.0070102572203</v>
       </c>
       <c r="O10" t="n">
-        <v>12.94970993218364</v>
+        <v>12.92311921546885</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0284636515415</v>
+        <v>338.0631522990296</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15325,28 +15389,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2489922987440199</v>
+        <v>-0.2544960451914496</v>
       </c>
       <c r="J11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02399086051905108</v>
+        <v>0.02526242513332499</v>
       </c>
       <c r="M11" t="n">
-        <v>9.866368483061089</v>
+        <v>9.853449028758815</v>
       </c>
       <c r="N11" t="n">
-        <v>158.7050044727461</v>
+        <v>158.1606602356958</v>
       </c>
       <c r="O11" t="n">
-        <v>12.59781744877842</v>
+        <v>12.57619418726094</v>
       </c>
       <c r="P11" t="n">
-        <v>343.4188220839064</v>
+        <v>343.4709704467007</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15403,28 +15467,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3399213375822049</v>
+        <v>-0.3420521618096464</v>
       </c>
       <c r="J12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04105234079052844</v>
+        <v>0.04195611675578137</v>
       </c>
       <c r="M12" t="n">
-        <v>10.74404612456278</v>
+        <v>10.70899076707691</v>
       </c>
       <c r="N12" t="n">
-        <v>169.8339714864021</v>
+        <v>169.0824457891563</v>
       </c>
       <c r="O12" t="n">
-        <v>13.0320363522514</v>
+        <v>13.00317060524687</v>
       </c>
       <c r="P12" t="n">
-        <v>351.1996402823259</v>
+        <v>351.2198299832732</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15481,28 +15545,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2116055288697138</v>
+        <v>-0.2139789370682631</v>
       </c>
       <c r="J13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01602794608461722</v>
+        <v>0.01654853977720849</v>
       </c>
       <c r="M13" t="n">
-        <v>10.23521690577833</v>
+        <v>10.20303334941134</v>
       </c>
       <c r="N13" t="n">
-        <v>172.9695463735206</v>
+        <v>172.2102622385925</v>
       </c>
       <c r="O13" t="n">
-        <v>13.1517887138412</v>
+        <v>13.122890772943</v>
       </c>
       <c r="P13" t="n">
-        <v>354.28894670903</v>
+        <v>354.3114349092004</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15559,28 +15623,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3541833720870291</v>
+        <v>-0.3584056292252067</v>
       </c>
       <c r="J14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0379964012331907</v>
+        <v>0.0392416346356308</v>
       </c>
       <c r="M14" t="n">
-        <v>11.21775261404975</v>
+        <v>11.19206978089289</v>
       </c>
       <c r="N14" t="n">
-        <v>199.8486882552229</v>
+        <v>199.0400417655069</v>
       </c>
       <c r="O14" t="n">
-        <v>14.13678493347136</v>
+        <v>14.10815515102903</v>
       </c>
       <c r="P14" t="n">
-        <v>359.1872766450899</v>
+        <v>359.227282811645</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15637,28 +15701,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6209088575611303</v>
+        <v>-0.6329610764568427</v>
       </c>
       <c r="J15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K15" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09278489447580307</v>
+        <v>0.09683913961100754</v>
       </c>
       <c r="M15" t="n">
-        <v>12.4483639036352</v>
+        <v>12.45714863055486</v>
       </c>
       <c r="N15" t="n">
-        <v>237.191673253493</v>
+        <v>236.4786404161725</v>
       </c>
       <c r="O15" t="n">
-        <v>15.40102831805373</v>
+        <v>15.37786202357703</v>
       </c>
       <c r="P15" t="n">
-        <v>365.5715561729968</v>
+        <v>365.6854625469484</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15696,7 +15760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P218"/>
+  <dimension ref="A1:P219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33566,12 +33630,94 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>-34.46452900602708,173.00296019461516</t>
+          <t>-34.464527603747165,173.0028855204011</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-34.45491384367711,173.00347123434014</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>-34.45565116351799,173.0032739844985</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-34.45638889358764,173.00309969799926</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-34.457129311245474,173.00307376689994</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-34.45786952465841,173.0030369509203</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-34.458610271157944,173.00302985032684</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-34.459342867026535,173.00298123085412</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-34.46006736381059,173.0029290367593</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-34.4608037870126,173.0029278429073</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-34.46154671067367,173.002918240612</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-34.46229562348735,173.00293840178094</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-34.46304443289012,173.0029557081304</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-34.4637874865945,173.00292376961107</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-34.46452732369455,173.0028706073295</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P219"/>
+  <dimension ref="A1:P220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12282,6 +12282,60 @@
       <c r="P219" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="C220" t="n">
+        <v>339.84</v>
+      </c>
+      <c r="D220" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="E220" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="F220" t="n">
+        <v>323.56</v>
+      </c>
+      <c r="G220" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="H220" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="I220" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="J220" t="n">
+        <v>326.21</v>
+      </c>
+      <c r="K220" t="n">
+        <v>332.05</v>
+      </c>
+      <c r="L220" t="n">
+        <v>340.78</v>
+      </c>
+      <c r="M220" t="n">
+        <v>344.37</v>
+      </c>
+      <c r="N220" t="n">
+        <v>343.01</v>
+      </c>
+      <c r="O220" t="n">
+        <v>340.32</v>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14519,6 +14573,16 @@
       </c>
       <c r="B222" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -14687,28 +14751,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3102317437289098</v>
+        <v>-0.3113009115535845</v>
       </c>
       <c r="J2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K2" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09142595210104676</v>
+        <v>0.0928594072039266</v>
       </c>
       <c r="M2" t="n">
-        <v>6.225005320982936</v>
+        <v>6.202458175864606</v>
       </c>
       <c r="N2" t="n">
-        <v>60.532279514085</v>
+        <v>60.26285634684695</v>
       </c>
       <c r="O2" t="n">
-        <v>7.780249322103052</v>
+        <v>7.762915454057641</v>
       </c>
       <c r="P2" t="n">
-        <v>362.9155139270673</v>
+        <v>362.9256961197535</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14765,28 +14829,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4767263670721363</v>
+        <v>-0.4783017056011269</v>
       </c>
       <c r="J3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1011302988876012</v>
+        <v>0.1026723563433721</v>
       </c>
       <c r="M3" t="n">
-        <v>9.005387804788946</v>
+        <v>8.972655898969961</v>
       </c>
       <c r="N3" t="n">
-        <v>127.8431672373184</v>
+        <v>127.2745617905088</v>
       </c>
       <c r="O3" t="n">
-        <v>11.30677528021666</v>
+        <v>11.28160280237293</v>
       </c>
       <c r="P3" t="n">
-        <v>354.45736404183</v>
+        <v>354.4723667383927</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14843,28 +14907,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4204226968241572</v>
+        <v>-0.4232654316447108</v>
       </c>
       <c r="J4" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K4" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06393857114805768</v>
+        <v>0.06536237560365987</v>
       </c>
       <c r="M4" t="n">
-        <v>10.42604827770781</v>
+        <v>10.38911166438823</v>
       </c>
       <c r="N4" t="n">
-        <v>163.7711715748207</v>
+        <v>163.0727017785743</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79731110721392</v>
+        <v>12.76999223878285</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9916507492156</v>
+        <v>342.0187234622458</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14921,28 +14985,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4962424223178754</v>
+        <v>-0.4988479002918567</v>
       </c>
       <c r="J5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08224169438470197</v>
+        <v>0.08381037364192767</v>
       </c>
       <c r="M5" t="n">
-        <v>10.48926824058564</v>
+        <v>10.45414123231095</v>
       </c>
       <c r="N5" t="n">
-        <v>173.9192986757172</v>
+        <v>173.1665975746675</v>
       </c>
       <c r="O5" t="n">
-        <v>13.1878466276992</v>
+        <v>13.1592780035482</v>
       </c>
       <c r="P5" t="n">
-        <v>340.6778862942193</v>
+        <v>340.7026994976832</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14999,28 +15063,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5981286022996789</v>
+        <v>-0.598543540398957</v>
       </c>
       <c r="J6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1118188031810459</v>
+        <v>0.1129913169006261</v>
       </c>
       <c r="M6" t="n">
-        <v>10.24751394956612</v>
+        <v>10.20301252521119</v>
       </c>
       <c r="N6" t="n">
-        <v>179.845510777766</v>
+        <v>179.0253496988512</v>
       </c>
       <c r="O6" t="n">
-        <v>13.41064915571823</v>
+        <v>13.38003548944663</v>
       </c>
       <c r="P6" t="n">
-        <v>340.0829634812432</v>
+        <v>340.0869151337174</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15077,28 +15141,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4155790599939577</v>
+        <v>-0.4167483274003642</v>
       </c>
       <c r="J7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0588087393224439</v>
+        <v>0.05969739116150186</v>
       </c>
       <c r="M7" t="n">
-        <v>9.901500039386024</v>
+        <v>9.86264002683985</v>
       </c>
       <c r="N7" t="n">
-        <v>174.9311109413073</v>
+        <v>174.1406868394031</v>
       </c>
       <c r="O7" t="n">
-        <v>13.22615253735217</v>
+        <v>13.19623760165764</v>
       </c>
       <c r="P7" t="n">
-        <v>335.6735385389532</v>
+        <v>335.6846740274694</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15155,28 +15219,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4431799502471531</v>
+        <v>-0.4443342176312715</v>
       </c>
       <c r="J8" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K8" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0552009556450106</v>
+        <v>0.05601678501230434</v>
       </c>
       <c r="M8" t="n">
-        <v>11.18750038048287</v>
+        <v>11.14245289231743</v>
       </c>
       <c r="N8" t="n">
-        <v>212.7535340263075</v>
+        <v>211.790191981896</v>
       </c>
       <c r="O8" t="n">
-        <v>14.58607329017332</v>
+        <v>14.55301315817092</v>
       </c>
       <c r="P8" t="n">
-        <v>333.5331587218545</v>
+        <v>333.5441513580386</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15233,28 +15297,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3242693797336912</v>
+        <v>-0.3278520636027562</v>
       </c>
       <c r="J9" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K9" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03348791569088005</v>
+        <v>0.03453714977382982</v>
       </c>
       <c r="M9" t="n">
-        <v>10.65580844415375</v>
+        <v>10.62294725377403</v>
       </c>
       <c r="N9" t="n">
-        <v>192.0678953681691</v>
+        <v>191.2692478479467</v>
       </c>
       <c r="O9" t="n">
-        <v>13.85885620706735</v>
+        <v>13.83001257584196</v>
       </c>
       <c r="P9" t="n">
-        <v>331.3645285239191</v>
+        <v>331.3986481229629</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15311,28 +15375,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3733098599932099</v>
+        <v>-0.3748906748508232</v>
       </c>
       <c r="J10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05016228982794457</v>
+        <v>0.05106228848177141</v>
       </c>
       <c r="M10" t="n">
-        <v>9.792170207400638</v>
+        <v>9.754047827927833</v>
       </c>
       <c r="N10" t="n">
-        <v>167.0070102572203</v>
+        <v>166.2596800145965</v>
       </c>
       <c r="O10" t="n">
-        <v>12.92311921546885</v>
+        <v>12.89417232762912</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0631522990296</v>
+        <v>338.0782071492691</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15389,28 +15453,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2544960451914496</v>
+        <v>-0.2584403275322132</v>
       </c>
       <c r="J11" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K11" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02526242513332499</v>
+        <v>0.02627980665588603</v>
       </c>
       <c r="M11" t="n">
-        <v>9.853449028758815</v>
+        <v>9.831336180256349</v>
       </c>
       <c r="N11" t="n">
-        <v>158.1606602356958</v>
+        <v>157.5334593235508</v>
       </c>
       <c r="O11" t="n">
-        <v>12.57619418726094</v>
+        <v>12.55123337857881</v>
       </c>
       <c r="P11" t="n">
-        <v>343.4709704467007</v>
+        <v>343.508533719627</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15467,28 +15531,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3420521618096464</v>
+        <v>-0.3431432401820339</v>
       </c>
       <c r="J12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04195611675578137</v>
+        <v>0.04263243917999893</v>
       </c>
       <c r="M12" t="n">
-        <v>10.70899076707691</v>
+        <v>10.66728999671881</v>
       </c>
       <c r="N12" t="n">
-        <v>169.0824457891563</v>
+        <v>168.3176487743877</v>
       </c>
       <c r="O12" t="n">
-        <v>13.00317060524687</v>
+        <v>12.97372917762613</v>
       </c>
       <c r="P12" t="n">
-        <v>351.2198299832732</v>
+        <v>351.2302208405053</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15545,28 +15609,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2139789370682631</v>
+        <v>-0.2175868565770968</v>
       </c>
       <c r="J13" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K13" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01654853977720849</v>
+        <v>0.01726901132789516</v>
       </c>
       <c r="M13" t="n">
-        <v>10.20303334941134</v>
+        <v>10.17860614725949</v>
       </c>
       <c r="N13" t="n">
-        <v>172.2102622385925</v>
+        <v>171.5033968410898</v>
       </c>
       <c r="O13" t="n">
-        <v>13.122890772943</v>
+        <v>13.09593054506207</v>
       </c>
       <c r="P13" t="n">
-        <v>354.3114349092004</v>
+        <v>354.34579483922</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15623,28 +15687,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3584056292252067</v>
+        <v>-0.3640793374207241</v>
       </c>
       <c r="J14" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K14" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0392416346356308</v>
+        <v>0.04080881719204676</v>
       </c>
       <c r="M14" t="n">
-        <v>11.19206978089289</v>
+        <v>11.17539126550073</v>
       </c>
       <c r="N14" t="n">
-        <v>199.0400417655069</v>
+        <v>198.3277424485544</v>
       </c>
       <c r="O14" t="n">
-        <v>14.10815515102903</v>
+        <v>14.08288828502713</v>
       </c>
       <c r="P14" t="n">
-        <v>359.227282811645</v>
+        <v>359.2813162278764</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15701,28 +15765,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6329610764568427</v>
+        <v>-0.6401715917752189</v>
       </c>
       <c r="J15" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K15" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09683913961100754</v>
+        <v>0.0996453509041223</v>
       </c>
       <c r="M15" t="n">
-        <v>12.45714863055486</v>
+        <v>12.44539883960272</v>
       </c>
       <c r="N15" t="n">
-        <v>236.4786404161725</v>
+        <v>235.7162916468286</v>
       </c>
       <c r="O15" t="n">
-        <v>15.37786202357703</v>
+        <v>15.35305479853533</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6854625469484</v>
+        <v>365.7541317068724</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15760,7 +15824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P219"/>
+  <dimension ref="A1:P220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33721,6 +33785,88 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-34.4549142784833,173.00349517999507</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>-34.455652151791696,173.003328406918</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>-34.45639023180512,173.003173386601</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-34.457130155303346,173.00312024446325</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-34.45787052488826,173.0030920278628</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-34.45861096499588,173.0030680562112</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-34.459344038989364,173.0030174588709</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-34.460068520521396,173.00294825727423</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-34.46080562031171,173.0029526774598</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-34.46154803160735,173.00293613466226</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-34.462296352407,173.00295056450128</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-34.463043896905425,173.0029391709374</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-34.46378711251422,173.0029038494064</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-34.464527015021304,173.00285417029448</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
